--- a/2022 data/excel_outputs/23_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/23_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="415">
   <si>
     <t>AC 23 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -454,7 +520,7 @@
     <t>PURV. MA V. SIAU ROOM-2</t>
   </si>
   <si>
-    <t>PURV. MA V. SIAU ROOM-■</t>
+    <t>CHTANAPANCHAMKANAP TVAVAU CHAVAN 2</t>
   </si>
   <si>
     <t>KANYA J.H. SCHOOL SIAU ROOM-1</t>
@@ -1199,8 +1265,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1216,7 +1290,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1224,12 +1298,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1528,79 +1620,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="E2" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="F2" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="G2" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="H2" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="I2" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="J2" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="K2" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="L2" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="M2" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="N2" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="O2" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="P2" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="Q2" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="R2" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="S2" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="T2" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="U2" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="V2" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="W2" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1608,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>1225</v>
@@ -1679,7 +1837,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1087</v>
@@ -1750,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>626</v>
@@ -1821,7 +1979,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1192</v>
@@ -1892,7 +2050,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>860</v>
@@ -1963,7 +2121,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>788</v>
@@ -2034,7 +2192,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>501</v>
@@ -2105,7 +2263,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1137</v>
@@ -2176,7 +2334,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>956</v>
@@ -2247,7 +2405,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>930</v>
@@ -2318,7 +2476,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>873</v>
@@ -2389,7 +2547,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>1071</v>
@@ -2460,7 +2618,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1007</v>
@@ -2531,7 +2689,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>1065</v>
@@ -2602,7 +2760,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1219</v>
@@ -2673,7 +2831,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>839</v>
@@ -2744,7 +2902,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>813</v>
@@ -2815,7 +2973,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>782</v>
@@ -2886,7 +3044,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>714</v>
@@ -2957,7 +3115,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>692</v>
@@ -3028,7 +3186,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>674</v>
@@ -3099,7 +3257,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>1009</v>
@@ -3170,7 +3328,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>620</v>
@@ -3241,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>1187</v>
@@ -3312,7 +3470,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>580</v>
@@ -3383,7 +3541,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>781</v>
@@ -3454,7 +3612,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>1057</v>
@@ -3525,7 +3683,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>1258</v>
@@ -3596,7 +3754,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>854</v>
@@ -3667,7 +3825,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1006</v>
@@ -3738,7 +3896,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>1012</v>
@@ -3809,7 +3967,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>1044</v>
@@ -3880,7 +4038,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>547</v>
@@ -3951,7 +4109,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>739</v>
@@ -4022,7 +4180,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>799</v>
@@ -4093,7 +4251,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>1119</v>
@@ -4164,7 +4322,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>1086</v>
@@ -4235,7 +4393,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>1058</v>
@@ -4306,7 +4464,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>987</v>
@@ -4377,7 +4535,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>726</v>
@@ -4448,7 +4606,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>479</v>
@@ -4519,7 +4677,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>697</v>
@@ -4590,7 +4748,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>674</v>
@@ -4661,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>1033</v>
@@ -4732,7 +4890,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>635</v>
@@ -4803,7 +4961,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>504</v>
@@ -4874,7 +5032,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>924</v>
@@ -4945,7 +5103,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>644</v>
@@ -5016,7 +5174,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>804</v>
@@ -5087,7 +5245,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>725</v>
@@ -5158,7 +5316,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>637</v>
@@ -5229,7 +5387,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>717</v>
@@ -5300,7 +5458,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>731</v>
@@ -5371,7 +5529,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>705</v>
@@ -5442,7 +5600,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>858</v>
@@ -5513,7 +5671,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>464</v>
@@ -5584,7 +5742,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>751</v>
@@ -5655,7 +5813,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>1009</v>
@@ -5726,7 +5884,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>888</v>
@@ -5797,7 +5955,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>750</v>
@@ -5868,7 +6026,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>1168</v>
@@ -5939,7 +6097,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>1177</v>
@@ -6010,7 +6168,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>871</v>
@@ -6081,7 +6239,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>694</v>
@@ -6152,7 +6310,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>821</v>
@@ -6223,7 +6381,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>901</v>
@@ -6294,7 +6452,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>1183</v>
@@ -6365,7 +6523,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>895</v>
@@ -6436,7 +6594,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>667</v>
@@ -6507,7 +6665,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>1060</v>
@@ -6578,7 +6736,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>1066</v>
@@ -6649,7 +6807,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>1200</v>
@@ -6720,7 +6878,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>991</v>
@@ -6791,7 +6949,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>444</v>
@@ -6862,7 +7020,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>990</v>
@@ -6933,7 +7091,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>437</v>
@@ -7004,7 +7162,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>664</v>
@@ -7075,7 +7233,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>646</v>
@@ -7146,7 +7304,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>746</v>
@@ -7217,7 +7375,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>448</v>
@@ -7288,7 +7446,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>965</v>
@@ -7359,7 +7517,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>657</v>
@@ -7430,7 +7588,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>550</v>
@@ -7501,7 +7659,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>1107</v>
@@ -7572,7 +7730,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>1114</v>
@@ -7643,7 +7801,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>1231</v>
@@ -7714,7 +7872,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>1141</v>
@@ -7785,7 +7943,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>455</v>
@@ -7856,7 +8014,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>659</v>
@@ -7927,7 +8085,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>574</v>
@@ -7998,7 +8156,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>418</v>
@@ -8069,7 +8227,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>1131</v>
@@ -8140,7 +8298,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>1130</v>
@@ -8211,7 +8369,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>487</v>
@@ -8282,7 +8440,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>482</v>
@@ -8353,7 +8511,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>677</v>
@@ -8424,7 +8582,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>664</v>
@@ -8495,7 +8653,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>649</v>
@@ -8566,7 +8724,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>572</v>
@@ -8637,7 +8795,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>860</v>
@@ -8708,7 +8866,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>1041</v>
@@ -8779,7 +8937,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>987</v>
@@ -8850,7 +9008,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>1081</v>
@@ -8921,7 +9079,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>757</v>
@@ -8992,7 +9150,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>944</v>
@@ -9063,7 +9221,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>598</v>
@@ -9134,7 +9292,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>1174</v>
@@ -9205,7 +9363,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>988</v>
@@ -9276,7 +9434,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>936</v>
@@ -9347,7 +9505,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>769</v>
@@ -9418,7 +9576,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>1140</v>
@@ -9489,7 +9647,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>745</v>
@@ -9560,7 +9718,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>686</v>
@@ -9631,7 +9789,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>1117</v>
@@ -9702,7 +9860,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>689</v>
@@ -9773,7 +9931,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>700</v>
@@ -9844,7 +10002,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>1165</v>
@@ -9915,7 +10073,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>1135</v>
@@ -9986,7 +10144,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C121">
         <v>1040</v>
@@ -10057,7 +10215,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>713</v>
@@ -10128,7 +10286,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>922</v>
@@ -10199,7 +10357,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>954</v>
@@ -10270,7 +10428,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>1019</v>
@@ -10341,7 +10499,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>1067</v>
@@ -10412,7 +10570,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>642</v>
@@ -10483,7 +10641,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>714</v>
@@ -10554,7 +10712,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>449</v>
@@ -10625,7 +10783,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>640</v>
@@ -10696,7 +10854,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>1153</v>
@@ -10767,7 +10925,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>1136</v>
@@ -10838,7 +10996,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C133">
         <v>737</v>
@@ -10909,7 +11067,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C134">
         <v>1187</v>
@@ -10980,7 +11138,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C135">
         <v>697</v>
@@ -11051,7 +11209,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C136">
         <v>631</v>
@@ -11122,7 +11280,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C137">
         <v>700</v>
@@ -11193,7 +11351,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C138">
         <v>562</v>
@@ -11264,7 +11422,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C139">
         <v>732</v>
@@ -11335,7 +11493,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C140">
         <v>615</v>
@@ -11406,7 +11564,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C141">
         <v>756</v>
@@ -11477,7 +11635,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C142">
         <v>710</v>
@@ -11548,7 +11706,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C143">
         <v>826</v>
@@ -11619,7 +11777,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C144">
         <v>704</v>
@@ -11690,7 +11848,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C145">
         <v>755</v>
@@ -11761,7 +11919,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C146">
         <v>1154</v>
@@ -11832,7 +11990,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C147">
         <v>1061</v>
@@ -11903,7 +12061,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C148">
         <v>939</v>
@@ -11974,7 +12132,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C149">
         <v>1098</v>
@@ -12045,7 +12203,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C150">
         <v>687</v>
@@ -12116,7 +12274,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C151">
         <v>1021</v>
@@ -12187,7 +12345,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C152">
         <v>621</v>
@@ -12258,7 +12416,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C153">
         <v>939</v>
@@ -12329,7 +12487,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C154">
         <v>992</v>
@@ -12400,7 +12558,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C155">
         <v>995</v>
@@ -12471,7 +12629,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C156">
         <v>847</v>
@@ -12542,7 +12700,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C157">
         <v>1084</v>
@@ -12613,7 +12771,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C158">
         <v>1230</v>
@@ -12684,7 +12842,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C159">
         <v>1074</v>
@@ -12755,7 +12913,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C160">
         <v>1143</v>
@@ -12826,7 +12984,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C161">
         <v>966</v>
@@ -12897,7 +13055,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C162">
         <v>965</v>
@@ -12968,7 +13126,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C163">
         <v>1103</v>
@@ -13039,7 +13197,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C164">
         <v>982</v>
@@ -13110,7 +13268,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C165">
         <v>823</v>
@@ -13181,7 +13339,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C166">
         <v>824</v>
@@ -13252,7 +13410,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C167">
         <v>901</v>
@@ -13323,7 +13481,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C168">
         <v>970</v>
@@ -13394,7 +13552,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C169">
         <v>1153</v>
@@ -13465,7 +13623,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C170">
         <v>1172</v>
@@ -13536,7 +13694,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C171">
         <v>816</v>
@@ -13607,7 +13765,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C172">
         <v>1070</v>
@@ -13678,7 +13836,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C173">
         <v>1048</v>
@@ -13749,7 +13907,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C174">
         <v>1034</v>
@@ -13820,7 +13978,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C175">
         <v>765</v>
@@ -13891,7 +14049,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C176">
         <v>1179</v>
@@ -13962,7 +14120,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C177">
         <v>798</v>
@@ -14033,7 +14191,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C178">
         <v>1129</v>
@@ -14104,7 +14262,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C179">
         <v>1227</v>
@@ -14175,7 +14333,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C180">
         <v>662</v>
@@ -14246,7 +14404,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C181">
         <v>619</v>
@@ -14317,7 +14475,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C182">
         <v>1092</v>
@@ -14388,7 +14546,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C183">
         <v>801</v>
@@ -14459,7 +14617,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C184">
         <v>1192</v>
@@ -14530,7 +14688,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C185">
         <v>957</v>
@@ -14601,7 +14759,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C186">
         <v>1079</v>
@@ -14672,7 +14830,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C187">
         <v>1177</v>
@@ -14743,7 +14901,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C188">
         <v>1191</v>
@@ -14814,7 +14972,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C189">
         <v>1211</v>
@@ -14885,7 +15043,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C190">
         <v>872</v>
@@ -14956,7 +15114,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C191">
         <v>1169</v>
@@ -15027,7 +15185,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C192">
         <v>1151</v>
@@ -15098,7 +15256,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C193">
         <v>1158</v>
@@ -15169,7 +15327,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C194">
         <v>1156</v>
@@ -15240,7 +15398,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C195">
         <v>1137</v>
@@ -15311,7 +15469,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C196">
         <v>1074</v>
@@ -15382,7 +15540,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C197">
         <v>1075</v>
@@ -15453,7 +15611,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C198">
         <v>1146</v>
@@ -15524,7 +15682,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C199">
         <v>1147</v>
@@ -15595,7 +15753,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C200">
         <v>731</v>
@@ -15666,7 +15824,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C201">
         <v>1137</v>
@@ -15737,7 +15895,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C202">
         <v>788</v>
@@ -15808,7 +15966,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C203">
         <v>718</v>
@@ -15879,7 +16037,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C204">
         <v>1146</v>
@@ -15950,7 +16108,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C205">
         <v>1122</v>
@@ -16021,7 +16179,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C206">
         <v>1121</v>
@@ -16092,7 +16250,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C207">
         <v>1167</v>
@@ -16163,7 +16321,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C208">
         <v>1071</v>
@@ -16234,7 +16392,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C209">
         <v>1110</v>
@@ -16305,7 +16463,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C210">
         <v>963</v>
@@ -16376,7 +16534,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C211">
         <v>1150</v>
@@ -16447,7 +16605,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C212">
         <v>739</v>
@@ -16518,7 +16676,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C213">
         <v>873</v>
@@ -16589,7 +16747,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C214">
         <v>844</v>
@@ -16660,7 +16818,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C215">
         <v>931</v>
@@ -16731,7 +16889,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C216">
         <v>1112</v>
@@ -16802,7 +16960,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C217">
         <v>804</v>
@@ -16873,7 +17031,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C218">
         <v>605</v>
@@ -16944,7 +17102,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C219">
         <v>755</v>
@@ -17015,7 +17173,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C220">
         <v>766</v>
@@ -17086,7 +17244,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C221">
         <v>777</v>
@@ -17157,7 +17315,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C222">
         <v>1114</v>
@@ -17228,7 +17386,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C223">
         <v>825</v>
@@ -17299,7 +17457,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C224">
         <v>470</v>
@@ -17370,7 +17528,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C225">
         <v>1012</v>
@@ -17441,7 +17599,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C226">
         <v>1135</v>
@@ -17512,7 +17670,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C227">
         <v>1091</v>
@@ -17583,7 +17741,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C228">
         <v>812</v>
@@ -17654,7 +17812,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C229">
         <v>1115</v>
@@ -17725,7 +17883,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C230">
         <v>1023</v>
@@ -17796,7 +17954,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C231">
         <v>1047</v>
@@ -17867,7 +18025,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C232">
         <v>864</v>
@@ -17938,7 +18096,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C233">
         <v>1117</v>
@@ -18009,7 +18167,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C234">
         <v>790</v>
@@ -18080,7 +18238,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C235">
         <v>881</v>
@@ -18151,7 +18309,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C236">
         <v>777</v>
@@ -18222,7 +18380,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C237">
         <v>738</v>
@@ -18293,7 +18451,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C238">
         <v>411</v>
@@ -18364,7 +18522,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C239">
         <v>745</v>
@@ -18435,7 +18593,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C240">
         <v>952</v>
@@ -18506,7 +18664,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C241">
         <v>913</v>
@@ -18577,7 +18735,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C242">
         <v>1024</v>
@@ -18648,7 +18806,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C243">
         <v>977</v>
@@ -18719,7 +18877,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C244">
         <v>655</v>
@@ -18790,7 +18948,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C245">
         <v>1089</v>
@@ -18861,7 +19019,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C246">
         <v>992</v>
@@ -18932,7 +19090,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C247">
         <v>734</v>
@@ -19003,7 +19161,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C248">
         <v>432</v>
@@ -19074,7 +19232,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C249">
         <v>708</v>
@@ -19145,7 +19303,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C250">
         <v>871</v>
@@ -19216,7 +19374,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C251">
         <v>1019</v>
@@ -19287,7 +19445,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C252">
         <v>655</v>
@@ -19358,7 +19516,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C253">
         <v>810</v>
@@ -19429,7 +19587,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C254">
         <v>480</v>
@@ -19500,7 +19658,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C255">
         <v>660</v>
@@ -19571,7 +19729,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C256">
         <v>801</v>
@@ -19642,7 +19800,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C257">
         <v>744</v>
@@ -19713,7 +19871,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C258">
         <v>655</v>
@@ -19784,7 +19942,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C259">
         <v>921</v>
@@ -19855,7 +20013,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C260">
         <v>784</v>
@@ -19926,7 +20084,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C261">
         <v>818</v>
@@ -19997,7 +20155,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C262">
         <v>546</v>
@@ -20068,7 +20226,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C263">
         <v>1020</v>
@@ -20139,7 +20297,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C264">
         <v>572</v>
@@ -20210,7 +20368,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C265">
         <v>683</v>
@@ -20281,7 +20439,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C266">
         <v>914</v>
@@ -20352,7 +20510,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C267">
         <v>944</v>
@@ -20423,7 +20581,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C268">
         <v>805</v>
@@ -20494,7 +20652,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C269">
         <v>802</v>
@@ -20565,7 +20723,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C270">
         <v>691</v>
@@ -20636,7 +20794,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C271">
         <v>1176</v>
@@ -20707,7 +20865,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C272">
         <v>782</v>
@@ -20778,7 +20936,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C273">
         <v>586</v>
@@ -20849,7 +21007,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>449</v>
@@ -20920,7 +21078,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>881</v>
@@ -20991,7 +21149,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>824</v>
@@ -21062,7 +21220,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>568</v>
@@ -21133,7 +21291,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>516</v>
@@ -21204,7 +21362,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>688</v>
@@ -21275,7 +21433,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>1009</v>
@@ -21346,7 +21504,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>981</v>
@@ -21417,7 +21575,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>989</v>
@@ -21488,7 +21646,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>824</v>
@@ -21559,7 +21717,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>608</v>
@@ -21630,7 +21788,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>736</v>
@@ -21701,7 +21859,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>708</v>
@@ -21772,7 +21930,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>975</v>
@@ -21843,7 +22001,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>868</v>
@@ -21914,7 +22072,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>703</v>
@@ -21985,7 +22143,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>877</v>
@@ -22056,7 +22214,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>992</v>
@@ -22127,7 +22285,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>1073</v>
@@ -22198,7 +22356,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>1020</v>
@@ -22269,7 +22427,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>809</v>
@@ -22340,7 +22498,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>1043</v>
@@ -22411,7 +22569,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>564</v>
@@ -22482,7 +22640,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>773</v>
@@ -22553,7 +22711,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>625</v>
@@ -22624,7 +22782,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>780</v>
@@ -22695,7 +22853,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>719</v>
@@ -22766,7 +22924,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>650</v>
@@ -22837,7 +22995,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C302">
         <v>763</v>
@@ -22908,7 +23066,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C303">
         <v>1098</v>
@@ -22979,7 +23137,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C304">
         <v>951</v>
@@ -23050,7 +23208,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C305">
         <v>847</v>
@@ -23121,7 +23279,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C306">
         <v>738</v>
@@ -23192,7 +23350,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C307">
         <v>539</v>
@@ -23263,7 +23421,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C308">
         <v>1088</v>
@@ -23334,7 +23492,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C309">
         <v>1096</v>
@@ -23405,7 +23563,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C310">
         <v>626</v>
@@ -23476,7 +23634,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C311">
         <v>640</v>
@@ -23547,7 +23705,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C312">
         <v>1105</v>
@@ -23618,7 +23776,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C313">
         <v>960</v>
@@ -23689,7 +23847,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C314">
         <v>765</v>
@@ -23760,7 +23918,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C315">
         <v>784</v>
@@ -23831,7 +23989,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C316">
         <v>682</v>
@@ -23902,7 +24060,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C317">
         <v>1115</v>
@@ -23973,7 +24131,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C318">
         <v>953</v>
@@ -24044,7 +24202,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C319">
         <v>1153</v>
@@ -24115,7 +24273,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C320">
         <v>1049</v>
@@ -24186,7 +24344,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C321">
         <v>798</v>
@@ -24257,7 +24415,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C322">
         <v>939</v>
@@ -24328,7 +24486,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C323">
         <v>919</v>
@@ -24399,7 +24557,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C324">
         <v>674</v>
@@ -24470,7 +24628,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C325">
         <v>519</v>
@@ -24541,7 +24699,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C326">
         <v>734</v>
@@ -24612,7 +24770,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C327">
         <v>716</v>
@@ -24683,7 +24841,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C328">
         <v>968</v>
@@ -24754,7 +24912,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C329">
         <v>1187</v>
@@ -24825,7 +24983,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C330">
         <v>644</v>
@@ -24896,7 +25054,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C331">
         <v>631</v>
@@ -24967,7 +25125,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C332">
         <v>1172</v>
@@ -25038,7 +25196,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C333">
         <v>1055</v>
@@ -25109,7 +25267,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C334">
         <v>1011</v>
@@ -25180,7 +25338,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C335">
         <v>870</v>
@@ -25251,7 +25409,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C336">
         <v>966</v>
@@ -25322,7 +25480,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C337">
         <v>707</v>
@@ -25393,7 +25551,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C338">
         <v>712</v>
@@ -25464,7 +25622,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C339">
         <v>957</v>
@@ -25535,7 +25693,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C340">
         <v>517</v>
@@ -25606,7 +25764,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C341">
         <v>671</v>
@@ -25677,7 +25835,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C342">
         <v>656</v>
@@ -25748,7 +25906,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C343">
         <v>768</v>
@@ -25819,7 +25977,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C344">
         <v>774</v>
@@ -25890,7 +26048,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C345">
         <v>632</v>
@@ -25961,7 +26119,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C346">
         <v>502</v>
@@ -26032,7 +26190,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C347">
         <v>811</v>
@@ -26103,7 +26261,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C348">
         <v>710</v>
@@ -26174,7 +26332,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C349">
         <v>1139</v>
@@ -26245,7 +26403,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C350">
         <v>1156</v>
@@ -26316,7 +26474,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>1026</v>
@@ -26387,7 +26545,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>995</v>
@@ -26458,7 +26616,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>1113</v>
@@ -26529,7 +26687,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C354">
         <v>1027</v>
@@ -26600,7 +26758,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C355">
         <v>1126</v>
@@ -26671,7 +26829,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C356">
         <v>1003</v>
@@ -26742,7 +26900,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C357">
         <v>1124</v>
@@ -26813,7 +26971,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C358">
         <v>1072</v>
@@ -26884,7 +27042,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C359">
         <v>1022</v>
@@ -26955,7 +27113,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C360">
         <v>699</v>
@@ -27026,7 +27184,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C361">
         <v>649</v>
@@ -27097,7 +27255,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C362">
         <v>1115</v>
@@ -27168,7 +27326,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C363">
         <v>736</v>
@@ -27239,7 +27397,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C364">
         <v>1104</v>
@@ -27310,7 +27468,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C365">
         <v>556</v>
@@ -27381,7 +27539,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C366">
         <v>717</v>
@@ -27452,7 +27610,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C367">
         <v>1117</v>
@@ -27523,7 +27681,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C368">
         <v>1039</v>
@@ -27594,7 +27752,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C369">
         <v>744</v>
@@ -27665,7 +27823,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C370">
         <v>914</v>
@@ -27736,7 +27894,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="C371">
         <v>1100</v>
@@ -27807,7 +27965,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C372">
         <v>1136</v>
@@ -27878,7 +28036,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C373">
         <v>1114</v>
